--- a/data/trans_orig/P6709-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P6709-Clase-trans_orig.xlsx
@@ -505,7 +505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W46"/>
+  <dimension ref="A1:W40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -536,7 +536,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si tiene influencia sobre el orden en el que realizan las tareas en 2012</t>
+          <t>Población según si tiene influencia sobre el orden en el que realizan las tareas en 2012 (tasa de respuesta: 98,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1766</t>
+          <t>1772</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10437</t>
+          <t>11107</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2940</t>
+          <t>2842</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13753</t>
+          <t>12832</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5968</t>
+          <t>6608</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>19309</t>
+          <t>20133</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>4,05%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3142</t>
+          <t>3678</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16832</t>
+          <t>16799</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6307</t>
+          <t>5971</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>21745</t>
+          <t>21074</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>11822</t>
+          <t>11785</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>32737</t>
+          <t>31174</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,27%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>40714</t>
+          <t>40130</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>68352</t>
+          <t>68538</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>22,63%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>25153</t>
+          <t>24092</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>47821</t>
+          <t>47523</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>24,44%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>73640</t>
+          <t>72981</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>109562</t>
+          <t>108920</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>21,91%</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>60507</t>
+          <t>60247</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>93627</t>
+          <t>92617</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>19,9%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,92%</t>
+          <t>30,59%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1105,12 +1105,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>38065</t>
+          <t>37725</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>63743</t>
+          <t>63472</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1120,12 +1120,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>19,4%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>32,79%</t>
+          <t>32,65%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>105484</t>
+          <t>106074</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>147415</t>
+          <t>146155</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>21,33%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>29,65%</t>
+          <t>29,39%</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>142427</t>
+          <t>145402</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>180468</t>
+          <t>180962</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>47,04%</t>
+          <t>48,02%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>59,6%</t>
+          <t>59,76%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1218,12 +1218,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>74931</t>
+          <t>75909</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>104988</t>
+          <t>104302</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>38,54%</t>
+          <t>39,05%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>54,0%</t>
+          <t>53,65%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1253,12 +1253,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>228178</t>
+          <t>228699</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>274620</t>
+          <t>274412</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1268,12 +1268,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>45,89%</t>
+          <t>46,0%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>55,23%</t>
+          <t>55,19%</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8835</t>
+          <t>9675</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>29198</t>
+          <t>29840</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14635</t>
+          <t>14918</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>34441</t>
+          <t>33606</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>26315</t>
+          <t>27616</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>53731</t>
+          <t>56018</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>13,32%</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8795</t>
+          <t>8847</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>24874</t>
+          <t>25406</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1541,12 +1541,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7791</t>
+          <t>7845</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>24457</t>
+          <t>25341</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>19836</t>
+          <t>19610</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>41628</t>
+          <t>43554</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1611,12 +1611,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>10,36%</t>
         </is>
       </c>
     </row>
@@ -1639,12 +1639,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>45662</t>
+          <t>44061</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>73839</t>
+          <t>72181</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>28,14%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>20671</t>
+          <t>20334</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>42091</t>
+          <t>41375</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>25,67%</t>
+          <t>25,23%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>69773</t>
+          <t>69842</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>104376</t>
+          <t>106005</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1724,12 +1724,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>25,21%</t>
         </is>
       </c>
     </row>
@@ -1752,12 +1752,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>62767</t>
+          <t>63103</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>94777</t>
+          <t>95056</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1767,12 +1767,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>24,6%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>36,95%</t>
+          <t>37,06%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1787,12 +1787,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>39965</t>
+          <t>41609</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>64445</t>
+          <t>65913</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1802,12 +1802,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>24,37%</t>
+          <t>25,37%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>39,3%</t>
+          <t>40,19%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1822,12 +1822,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>112966</t>
+          <t>112887</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>152507</t>
+          <t>152420</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>26,86%</t>
+          <t>26,85%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>36,27%</t>
+          <t>36,25%</t>
         </is>
       </c>
     </row>
@@ -1865,12 +1865,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>73882</t>
+          <t>73083</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>105936</t>
+          <t>105059</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1880,12 +1880,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>28,8%</t>
+          <t>28,49%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>41,3%</t>
+          <t>40,96%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>33450</t>
+          <t>33515</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>57272</t>
+          <t>56049</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1915,12 +1915,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>20,44%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>34,92%</t>
+          <t>34,18%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1935,12 +1935,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>113423</t>
+          <t>112628</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>155500</t>
+          <t>153638</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1950,12 +1950,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>26,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>36,98%</t>
+          <t>36,54%</t>
         </is>
       </c>
     </row>
@@ -2095,12 +2095,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4739</t>
+          <t>4213</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16834</t>
+          <t>16014</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>985</t>
+          <t>1016</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9178</t>
+          <t>10039</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2145,12 +2145,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6754</t>
+          <t>7429</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>20737</t>
+          <t>22602</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,79%</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12653</t>
+          <t>12518</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>28436</t>
+          <t>28336</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2223,12 +2223,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2248,7 +2248,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7079</t>
+          <t>7109</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>14747</t>
+          <t>14661</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>32444</t>
+          <t>32334</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,29%</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>38414</t>
+          <t>37327</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>63133</t>
+          <t>64372</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2336,12 +2336,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>23,02%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2356,12 +2356,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>7188</t>
+          <t>7664</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>21857</t>
+          <t>22334</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2391,12 +2391,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>49365</t>
+          <t>47786</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>80339</t>
+          <t>78874</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>20,59%</t>
+          <t>20,22%</t>
         </is>
       </c>
     </row>
@@ -2434,12 +2434,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>52411</t>
+          <t>51584</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>79251</t>
+          <t>79483</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>28,43%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6899</t>
+          <t>7097</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>19993</t>
+          <t>21058</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>63010</t>
+          <t>63117</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>93560</t>
+          <t>94765</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>24,29%</t>
         </is>
       </c>
     </row>
@@ -2547,12 +2547,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>119802</t>
+          <t>118192</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>151685</t>
+          <t>152594</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2562,12 +2562,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>42,85%</t>
+          <t>42,28%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>54,26%</t>
+          <t>54,58%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2582,12 +2582,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>68841</t>
+          <t>69981</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>88286</t>
+          <t>87934</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2597,12 +2597,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>62,29%</t>
+          <t>63,32%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>79,88%</t>
+          <t>79,56%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>193315</t>
+          <t>193828</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>233301</t>
+          <t>233970</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2632,12 +2632,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>49,56%</t>
+          <t>49,69%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>59,81%</t>
+          <t>59,98%</t>
         </is>
       </c>
     </row>
@@ -2777,12 +2777,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>30210</t>
+          <t>29551</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>57094</t>
+          <t>55001</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2812,12 +2812,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>23921</t>
+          <t>24667</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>46856</t>
+          <t>47479</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2847,12 +2847,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>59856</t>
+          <t>58869</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>93485</t>
+          <t>92513</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>12,83%</t>
         </is>
       </c>
     </row>
@@ -2890,12 +2890,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>27098</t>
+          <t>25527</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>52327</t>
+          <t>51879</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2905,12 +2905,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2925,12 +2925,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>14511</t>
+          <t>13866</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>32416</t>
+          <t>34188</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2940,12 +2940,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2960,12 +2960,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>46436</t>
+          <t>45804</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>77853</t>
+          <t>78334</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2975,12 +2975,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,87%</t>
         </is>
       </c>
     </row>
@@ -3003,12 +3003,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>82431</t>
+          <t>82385</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>118903</t>
+          <t>118767</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3018,12 +3018,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>28,04%</t>
+          <t>28,01%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>61851</t>
+          <t>63321</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>92927</t>
+          <t>92319</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3053,12 +3053,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>21,33%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>31,31%</t>
+          <t>31,1%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>157424</t>
+          <t>153027</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>202552</t>
+          <t>202733</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3088,12 +3088,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>21,23%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>28,12%</t>
         </is>
       </c>
     </row>
@@ -3116,12 +3116,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>85391</t>
+          <t>85940</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>120709</t>
+          <t>119633</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3131,12 +3131,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>28,46%</t>
+          <t>28,21%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>48983</t>
+          <t>49495</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>78426</t>
+          <t>77711</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>26,18%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>141571</t>
+          <t>141456</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>188337</t>
+          <t>186670</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>25,89%</t>
         </is>
       </c>
     </row>
@@ -3229,12 +3229,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>123514</t>
+          <t>124294</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>164890</t>
+          <t>163631</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3244,12 +3244,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>29,31%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>38,88%</t>
+          <t>38,59%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3264,12 +3264,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>85406</t>
+          <t>85897</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>119509</t>
+          <t>119361</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>28,77%</t>
+          <t>28,94%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>40,26%</t>
+          <t>40,21%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>219414</t>
+          <t>220908</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>272135</t>
+          <t>274723</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>30,44%</t>
+          <t>30,64%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>37,75%</t>
+          <t>38,11%</t>
         </is>
       </c>
     </row>
@@ -3459,12 +3459,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>17552</t>
+          <t>17146</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>36231</t>
+          <t>35767</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3474,12 +3474,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>23,69%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>15955</t>
+          <t>15860</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>35520</t>
+          <t>33914</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3509,12 +3509,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>38961</t>
+          <t>38111</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>66729</t>
+          <t>64487</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>19,81%</t>
         </is>
       </c>
     </row>
@@ -3572,12 +3572,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>11564</t>
+          <t>11795</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>28256</t>
+          <t>27647</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3587,12 +3587,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>18,31%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3607,12 +3607,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>9690</t>
+          <t>10923</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>27406</t>
+          <t>28330</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3642,12 +3642,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>26870</t>
+          <t>26310</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>51089</t>
+          <t>49195</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>15,11%</t>
         </is>
       </c>
     </row>
@@ -3685,12 +3685,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>26485</t>
+          <t>26073</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>47693</t>
+          <t>47240</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>31,59%</t>
+          <t>31,29%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3720,12 +3720,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>29973</t>
+          <t>29078</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>54280</t>
+          <t>52524</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>31,09%</t>
+          <t>30,08%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3755,12 +3755,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>60590</t>
+          <t>61694</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>93315</t>
+          <t>92323</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>28,66%</t>
+          <t>28,36%</t>
         </is>
       </c>
     </row>
@@ -3798,12 +3798,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>24897</t>
+          <t>24183</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>45680</t>
+          <t>45282</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3813,12 +3813,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>30,25%</t>
+          <t>29,99%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>23325</t>
+          <t>24140</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>45037</t>
+          <t>45562</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>26,1%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>54904</t>
+          <t>54952</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>85875</t>
+          <t>85716</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>26,38%</t>
+          <t>26,33%</t>
         </is>
       </c>
     </row>
@@ -3911,12 +3911,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>26388</t>
+          <t>26090</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>47125</t>
+          <t>47398</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3926,12 +3926,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,28%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>31,21%</t>
+          <t>31,39%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3946,12 +3946,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>45894</t>
+          <t>45775</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>71777</t>
+          <t>72436</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>26,22%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>41,11%</t>
+          <t>41,49%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3981,12 +3981,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>78672</t>
+          <t>78154</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>112828</t>
+          <t>112245</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>34,65%</t>
+          <t>34,48%</t>
         </is>
       </c>
     </row>
@@ -4121,7 +4121,7 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -4131,107 +4131,107 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>87</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>97602</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>78148</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>118399</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>85</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>91047</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>71686</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>110813</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>172</t>
         </is>
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>188649</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>163329</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>219252</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>9,31%</t>
         </is>
       </c>
     </row>
@@ -4244,107 +4244,107 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>92</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>99167</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>81554</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>119531</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>61</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>68247</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>51743</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>88337</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>153</t>
         </is>
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>167413</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>141974</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>195651</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>8,31%</t>
         </is>
       </c>
     </row>
@@ -4357,107 +4357,107 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>281</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>296208</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>264048</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>329847</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>20,95%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>23,33%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>177</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>196235</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>169162</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>223138</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>23,73%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>458</t>
         </is>
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>492443</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>449692</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>533137</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>20,92%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>22,65%</t>
         </is>
       </c>
     </row>
@@ -4470,107 +4470,107 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>339</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>356282</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>323291</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>393347</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>25,2%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>27,82%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>200</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>210776</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>186191</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>237077</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>22,41%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>25,21%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>539</t>
         </is>
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>567058</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>525727</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>606867</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>24,09%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>25,78%</t>
         </is>
       </c>
     </row>
@@ -4583,107 +4583,107 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>528</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>564694</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>526995</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>603724</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>39,94%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>37,27%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>42,7%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>345</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>374046</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>343983</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>405738</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>39,78%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>36,58%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>43,15%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>873</t>
         </is>
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>938740</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>893456</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>989120</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>39,87%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>37,95%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>42,01%</t>
         </is>
       </c>
     </row>
@@ -4696,804 +4696,121 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1327</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1413953</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1413953</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1413953</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>868</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>940350</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>940350</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>940350</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2195</t>
         </is>
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2354303</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2354303</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2354303</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B40" s="3" t="inlineStr">
-        <is>
-          <t>Nunca</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>97602</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>79594</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>120522</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>6,9%</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>5,63%</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>8,52%</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t>91047</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="inlineStr">
-        <is>
-          <t>75015</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr">
-        <is>
-          <t>110431</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="inlineStr">
-        <is>
-          <t>9,68%</t>
-        </is>
-      </c>
-      <c r="O40" s="2" t="inlineStr">
-        <is>
-          <t>7,98%</t>
-        </is>
-      </c>
-      <c r="P40" s="2" t="inlineStr">
-        <is>
-          <t>11,74%</t>
-        </is>
-      </c>
-      <c r="Q40" s="2" t="inlineStr">
-        <is>
-          <t>172</t>
-        </is>
-      </c>
-      <c r="R40" s="2" t="inlineStr">
-        <is>
-          <t>188649</t>
-        </is>
-      </c>
-      <c r="S40" s="2" t="inlineStr">
-        <is>
-          <t>160064</t>
-        </is>
-      </c>
-      <c r="T40" s="2" t="inlineStr">
-        <is>
-          <t>217943</t>
-        </is>
-      </c>
-      <c r="U40" s="2" t="inlineStr">
-        <is>
-          <t>8,01%</t>
-        </is>
-      </c>
-      <c r="V40" s="2" t="inlineStr">
-        <is>
-          <t>6,8%</t>
-        </is>
-      </c>
-      <c r="W40" s="2" t="inlineStr">
-        <is>
-          <t>9,26%</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="1" t="n"/>
-      <c r="B41" s="3" t="inlineStr">
-        <is>
-          <t>Solo alguna vez</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>99167</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>80968</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>121206</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>7,01%</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>5,73%</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>8,57%</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="K41" s="2" t="inlineStr">
-        <is>
-          <t>68247</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="inlineStr">
-        <is>
-          <t>52296</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr">
-        <is>
-          <t>88417</t>
-        </is>
-      </c>
-      <c r="N41" s="2" t="inlineStr">
-        <is>
-          <t>7,26%</t>
-        </is>
-      </c>
-      <c r="O41" s="2" t="inlineStr">
-        <is>
-          <t>5,56%</t>
-        </is>
-      </c>
-      <c r="P41" s="2" t="inlineStr">
-        <is>
-          <t>9,4%</t>
-        </is>
-      </c>
-      <c r="Q41" s="2" t="inlineStr">
-        <is>
-          <t>153</t>
-        </is>
-      </c>
-      <c r="R41" s="2" t="inlineStr">
-        <is>
-          <t>167413</t>
-        </is>
-      </c>
-      <c r="S41" s="2" t="inlineStr">
-        <is>
-          <t>142534</t>
-        </is>
-      </c>
-      <c r="T41" s="2" t="inlineStr">
-        <is>
-          <t>194745</t>
-        </is>
-      </c>
-      <c r="U41" s="2" t="inlineStr">
-        <is>
-          <t>7,11%</t>
-        </is>
-      </c>
-      <c r="V41" s="2" t="inlineStr">
-        <is>
-          <t>6,05%</t>
-        </is>
-      </c>
-      <c r="W41" s="2" t="inlineStr">
-        <is>
-          <t>8,27%</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="1" t="n"/>
-      <c r="B42" s="3" t="inlineStr">
-        <is>
-          <t>Algunas veces</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>281</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>296208</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>265252</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>328253</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>20,95%</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>18,76%</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>23,22%</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>177</t>
-        </is>
-      </c>
-      <c r="K42" s="2" t="inlineStr">
-        <is>
-          <t>196235</t>
-        </is>
-      </c>
-      <c r="L42" s="2" t="inlineStr">
-        <is>
-          <t>167984</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr">
-        <is>
-          <t>223492</t>
-        </is>
-      </c>
-      <c r="N42" s="2" t="inlineStr">
-        <is>
-          <t>20,87%</t>
-        </is>
-      </c>
-      <c r="O42" s="2" t="inlineStr">
-        <is>
-          <t>17,86%</t>
-        </is>
-      </c>
-      <c r="P42" s="2" t="inlineStr">
-        <is>
-          <t>23,77%</t>
-        </is>
-      </c>
-      <c r="Q42" s="2" t="inlineStr">
-        <is>
-          <t>458</t>
-        </is>
-      </c>
-      <c r="R42" s="2" t="inlineStr">
-        <is>
-          <t>492443</t>
-        </is>
-      </c>
-      <c r="S42" s="2" t="inlineStr">
-        <is>
-          <t>452047</t>
-        </is>
-      </c>
-      <c r="T42" s="2" t="inlineStr">
-        <is>
-          <t>536118</t>
-        </is>
-      </c>
-      <c r="U42" s="2" t="inlineStr">
-        <is>
-          <t>20,92%</t>
-        </is>
-      </c>
-      <c r="V42" s="2" t="inlineStr">
-        <is>
-          <t>19,2%</t>
-        </is>
-      </c>
-      <c r="W42" s="2" t="inlineStr">
-        <is>
-          <t>22,77%</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="1" t="n"/>
-      <c r="B43" s="3" t="inlineStr">
-        <is>
-          <t>Muchas veces</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>339</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>356282</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>324434</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>393412</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>25,2%</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>22,95%</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>27,82%</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="K43" s="2" t="inlineStr">
-        <is>
-          <t>210776</t>
-        </is>
-      </c>
-      <c r="L43" s="2" t="inlineStr">
-        <is>
-          <t>184042</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr">
-        <is>
-          <t>241139</t>
-        </is>
-      </c>
-      <c r="N43" s="2" t="inlineStr">
-        <is>
-          <t>22,41%</t>
-        </is>
-      </c>
-      <c r="O43" s="2" t="inlineStr">
-        <is>
-          <t>19,57%</t>
-        </is>
-      </c>
-      <c r="P43" s="2" t="inlineStr">
-        <is>
-          <t>25,64%</t>
-        </is>
-      </c>
-      <c r="Q43" s="2" t="inlineStr">
-        <is>
-          <t>539</t>
-        </is>
-      </c>
-      <c r="R43" s="2" t="inlineStr">
-        <is>
-          <t>567058</t>
-        </is>
-      </c>
-      <c r="S43" s="2" t="inlineStr">
-        <is>
-          <t>523479</t>
-        </is>
-      </c>
-      <c r="T43" s="2" t="inlineStr">
-        <is>
-          <t>610284</t>
-        </is>
-      </c>
-      <c r="U43" s="2" t="inlineStr">
-        <is>
-          <t>24,09%</t>
-        </is>
-      </c>
-      <c r="V43" s="2" t="inlineStr">
-        <is>
-          <t>22,23%</t>
-        </is>
-      </c>
-      <c r="W43" s="2" t="inlineStr">
-        <is>
-          <t>25,92%</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="1" t="n"/>
-      <c r="B44" s="3" t="inlineStr">
-        <is>
-          <t>Siempre</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>528</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>564694</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>526027</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>603274</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>39,94%</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>37,2%</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>42,67%</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>345</t>
-        </is>
-      </c>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t>374046</t>
-        </is>
-      </c>
-      <c r="L44" s="2" t="inlineStr">
-        <is>
-          <t>341515</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr">
-        <is>
-          <t>405039</t>
-        </is>
-      </c>
-      <c r="N44" s="2" t="inlineStr">
-        <is>
-          <t>39,78%</t>
-        </is>
-      </c>
-      <c r="O44" s="2" t="inlineStr">
-        <is>
-          <t>36,32%</t>
-        </is>
-      </c>
-      <c r="P44" s="2" t="inlineStr">
-        <is>
-          <t>43,07%</t>
-        </is>
-      </c>
-      <c r="Q44" s="2" t="inlineStr">
-        <is>
-          <t>873</t>
-        </is>
-      </c>
-      <c r="R44" s="2" t="inlineStr">
-        <is>
-          <t>938740</t>
-        </is>
-      </c>
-      <c r="S44" s="2" t="inlineStr">
-        <is>
-          <t>890026</t>
-        </is>
-      </c>
-      <c r="T44" s="2" t="inlineStr">
-        <is>
-          <t>988726</t>
-        </is>
-      </c>
-      <c r="U44" s="2" t="inlineStr">
-        <is>
-          <t>39,87%</t>
-        </is>
-      </c>
-      <c r="V44" s="2" t="inlineStr">
-        <is>
-          <t>37,8%</t>
-        </is>
-      </c>
-      <c r="W44" s="2" t="inlineStr">
-        <is>
-          <t>42,0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="1" t="n"/>
-      <c r="B45" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>1327</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>1413953</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>1413953</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>1413953</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>868</t>
-        </is>
-      </c>
-      <c r="K45" s="2" t="inlineStr">
-        <is>
-          <t>940350</t>
-        </is>
-      </c>
-      <c r="L45" s="2" t="inlineStr">
-        <is>
-          <t>940350</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr">
-        <is>
-          <t>940350</t>
-        </is>
-      </c>
-      <c r="N45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q45" s="2" t="inlineStr">
-        <is>
-          <t>2195</t>
-        </is>
-      </c>
-      <c r="R45" s="2" t="inlineStr">
-        <is>
-          <t>2354303</t>
-        </is>
-      </c>
-      <c r="S45" s="2" t="inlineStr">
-        <is>
-          <t>2354303</t>
-        </is>
-      </c>
-      <c r="T45" s="2" t="inlineStr">
-        <is>
-          <t>2354303</t>
-        </is>
-      </c>
-      <c r="U45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
+      <c r="A40" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A22:A27"/>
-    <mergeCell ref="A40:A45"/>
     <mergeCell ref="A4:A9"/>
     <mergeCell ref="A16:A21"/>
     <mergeCell ref="A34:A39"/>
@@ -5513,7 +4830,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W46"/>
+  <dimension ref="A1:W40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5544,7 +4861,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si tiene influencia sobre el orden en el que realizan las tareas en 2016</t>
+          <t>Población según si tiene influencia sobre el orden en el que realizan las tareas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5739,12 +5056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4606</t>
+          <t>4928</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18122</t>
+          <t>17895</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5754,12 +5071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5774,12 +5091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5628</t>
+          <t>5122</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19622</t>
+          <t>18863</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5789,12 +5106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5809,12 +5126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12371</t>
+          <t>12337</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>30584</t>
+          <t>30865</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5824,12 +5141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,27%</t>
         </is>
       </c>
     </row>
@@ -5852,12 +5169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11370</t>
+          <t>11394</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>30060</t>
+          <t>29681</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5872,7 +5189,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5887,12 +5204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12581</t>
+          <t>13089</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>29931</t>
+          <t>31520</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5902,12 +5219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5922,12 +5239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>27110</t>
+          <t>27664</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>51601</t>
+          <t>52651</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5937,12 +5254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,69%</t>
         </is>
       </c>
     </row>
@@ -5965,12 +5282,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>63329</t>
+          <t>61448</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>95725</t>
+          <t>92584</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5980,12 +5297,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>22,08%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>34,39%</t>
+          <t>33,26%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6000,12 +5317,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>35348</t>
+          <t>35923</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>59071</t>
+          <t>60588</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6015,12 +5332,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>27,58%</t>
+          <t>28,29%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6035,12 +5352,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>105091</t>
+          <t>105726</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>142382</t>
+          <t>144290</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6050,12 +5367,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>29,3%</t>
         </is>
       </c>
     </row>
@@ -6078,12 +5395,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>50131</t>
+          <t>50602</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>81219</t>
+          <t>79497</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6093,12 +5410,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>18,18%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,18%</t>
+          <t>28,56%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6113,12 +5430,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>52680</t>
+          <t>52253</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>78444</t>
+          <t>78548</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6128,12 +5445,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>24,4%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>36,63%</t>
+          <t>36,67%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6148,12 +5465,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>110342</t>
+          <t>109512</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>148860</t>
+          <t>148283</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6163,12 +5480,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>30,22%</t>
+          <t>30,11%</t>
         </is>
       </c>
     </row>
@@ -6191,12 +5508,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>92989</t>
+          <t>91827</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>126507</t>
+          <t>125913</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6206,12 +5523,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>33,41%</t>
+          <t>32,99%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>45,45%</t>
+          <t>45,24%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6226,12 +5543,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>59825</t>
+          <t>58570</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>86965</t>
+          <t>86416</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6241,12 +5558,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>27,93%</t>
+          <t>27,35%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>40,6%</t>
+          <t>40,35%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6261,12 +5578,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>160534</t>
+          <t>159579</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>204990</t>
+          <t>204549</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6276,12 +5593,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>32,59%</t>
+          <t>32,4%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>41,62%</t>
+          <t>41,53%</t>
         </is>
       </c>
     </row>
@@ -6421,12 +5738,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10679</t>
+          <t>9584</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>30043</t>
+          <t>28012</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6436,12 +5753,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6456,12 +5773,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>13091</t>
+          <t>13594</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>29995</t>
+          <t>30817</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6471,12 +5788,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6491,12 +5808,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>27716</t>
+          <t>27061</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>52475</t>
+          <t>51853</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6506,12 +5823,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>11,97%</t>
         </is>
       </c>
     </row>
@@ -6534,12 +5851,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>33657</t>
+          <t>33014</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>58790</t>
+          <t>57320</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6549,12 +5866,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>23,49%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6569,12 +5886,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>27822</t>
+          <t>27953</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>50102</t>
+          <t>50739</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6584,12 +5901,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>26,48%</t>
+          <t>26,82%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6604,12 +5921,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>66859</t>
+          <t>66106</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>100594</t>
+          <t>100617</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6619,12 +5936,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>23,23%</t>
         </is>
       </c>
     </row>
@@ -6647,12 +5964,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>45658</t>
+          <t>45745</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>73745</t>
+          <t>73077</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6662,12 +5979,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>30,22%</t>
+          <t>29,95%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6682,12 +5999,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>32960</t>
+          <t>32796</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>56498</t>
+          <t>56549</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6697,12 +6014,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>29,87%</t>
+          <t>29,89%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6717,12 +6034,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>85371</t>
+          <t>86077</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>121081</t>
+          <t>122179</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6732,12 +6049,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>19,87%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>27,95%</t>
+          <t>28,2%</t>
         </is>
       </c>
     </row>
@@ -6760,12 +6077,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>52445</t>
+          <t>51756</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>81382</t>
+          <t>82156</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6775,12 +6092,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>21,21%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>33,35%</t>
+          <t>33,67%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6795,12 +6112,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>36354</t>
+          <t>36955</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>60459</t>
+          <t>60809</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6810,12 +6127,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,96%</t>
+          <t>32,14%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6830,12 +6147,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>96868</t>
+          <t>95160</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>135849</t>
+          <t>135134</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6845,12 +6162,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>21,97%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,36%</t>
+          <t>31,19%</t>
         </is>
       </c>
     </row>
@@ -6873,12 +6190,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>42784</t>
+          <t>44009</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>70908</t>
+          <t>69804</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6888,12 +6205,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>29,06%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6908,12 +6225,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>26409</t>
+          <t>27130</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>48668</t>
+          <t>49750</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6923,12 +6240,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>25,73%</t>
+          <t>26,3%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6943,12 +6260,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>77295</t>
+          <t>77651</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>112886</t>
+          <t>113591</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6958,12 +6275,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>26,22%</t>
         </is>
       </c>
     </row>
@@ -7103,12 +6420,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5986</t>
+          <t>6235</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20018</t>
+          <t>19697</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7118,12 +6435,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7143,7 +6460,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5022</t>
+          <t>4830</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7158,7 +6475,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7173,7 +6490,7 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>7293</t>
+          <t>7425</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
@@ -7188,7 +6505,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -7216,12 +6533,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13761</t>
+          <t>13360</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>31388</t>
+          <t>31223</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7231,12 +6548,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7251,12 +6568,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>827</t>
+          <t>850</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7805</t>
+          <t>7854</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7266,12 +6583,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7286,12 +6603,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>16445</t>
+          <t>16149</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>35536</t>
+          <t>35851</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7301,12 +6618,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,6%</t>
         </is>
       </c>
     </row>
@@ -7329,12 +6646,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>40385</t>
+          <t>39741</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>65157</t>
+          <t>65532</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7344,12 +6661,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>29,99%</t>
+          <t>30,16%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7364,12 +6681,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>5345</t>
+          <t>5107</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>16687</t>
+          <t>17112</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7379,12 +6696,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>25,46%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7399,12 +6716,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>48691</t>
+          <t>48754</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>75986</t>
+          <t>76036</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7414,12 +6731,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>26,73%</t>
         </is>
       </c>
     </row>
@@ -7442,12 +6759,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>46450</t>
+          <t>46873</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>73306</t>
+          <t>72977</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7457,12 +6774,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>21,57%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>33,74%</t>
+          <t>33,59%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7477,12 +6794,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>9437</t>
+          <t>8468</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>23079</t>
+          <t>22012</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7492,12 +6809,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>34,34%</t>
+          <t>32,76%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7512,12 +6829,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>60026</t>
+          <t>59896</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>89981</t>
+          <t>91177</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7527,12 +6844,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>31,63%</t>
+          <t>32,05%</t>
         </is>
       </c>
     </row>
@@ -7555,12 +6872,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>59289</t>
+          <t>59366</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>89729</t>
+          <t>87782</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7570,12 +6887,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>27,29%</t>
+          <t>27,32%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>41,3%</t>
+          <t>40,4%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7590,12 +6907,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>30080</t>
+          <t>30348</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>45961</t>
+          <t>46487</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7605,12 +6922,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>44,76%</t>
+          <t>45,16%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>68,39%</t>
+          <t>69,18%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7625,12 +6942,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>95221</t>
+          <t>94647</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>128766</t>
+          <t>128725</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7640,12 +6957,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>33,47%</t>
+          <t>33,27%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>45,27%</t>
+          <t>45,25%</t>
         </is>
       </c>
     </row>
@@ -7785,12 +7102,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>55611</t>
+          <t>56280</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>87502</t>
+          <t>86579</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7800,12 +7117,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7820,12 +7137,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>38139</t>
+          <t>37786</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>63964</t>
+          <t>64418</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7835,12 +7152,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7855,12 +7172,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>98935</t>
+          <t>98005</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>140231</t>
+          <t>138836</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7870,12 +7187,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,2%</t>
         </is>
       </c>
     </row>
@@ -7898,12 +7215,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>58841</t>
+          <t>58616</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>90773</t>
+          <t>91200</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7913,12 +7230,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>18,66%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7933,12 +7250,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>37826</t>
+          <t>39024</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>64890</t>
+          <t>65557</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7948,12 +7265,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -7968,12 +7285,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>104482</t>
+          <t>104230</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>146967</t>
+          <t>144389</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -7983,12 +7300,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>16,85%</t>
         </is>
       </c>
     </row>
@@ -8011,12 +7328,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>119973</t>
+          <t>122116</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>161069</t>
+          <t>163031</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8026,12 +7343,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>24,99%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>32,96%</t>
+          <t>33,36%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8046,12 +7363,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>98781</t>
+          <t>99236</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>135185</t>
+          <t>132212</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8061,12 +7378,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>26,96%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>36,73%</t>
+          <t>35,92%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8081,12 +7398,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>229736</t>
+          <t>230113</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>281975</t>
+          <t>283371</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -8096,12 +7413,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>26,81%</t>
+          <t>26,86%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>32,91%</t>
+          <t>33,07%</t>
         </is>
       </c>
     </row>
@@ -8124,12 +7441,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>88756</t>
+          <t>88931</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>123572</t>
+          <t>125391</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -8139,12 +7456,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>25,66%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -8159,12 +7476,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>52871</t>
+          <t>54213</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>82593</t>
+          <t>82991</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -8174,12 +7491,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>22,55%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -8194,12 +7511,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>148515</t>
+          <t>151446</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>197299</t>
+          <t>196951</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -8209,12 +7526,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>22,99%</t>
         </is>
       </c>
     </row>
@@ -8237,12 +7554,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>82422</t>
+          <t>82182</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>119303</t>
+          <t>118067</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -8252,12 +7569,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>24,16%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8272,12 +7589,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>71780</t>
+          <t>71454</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>105336</t>
+          <t>103664</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -8287,12 +7604,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>28,17%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -8307,12 +7624,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>161795</t>
+          <t>161393</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>210840</t>
+          <t>212060</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -8322,12 +7639,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>24,75%</t>
         </is>
       </c>
     </row>
@@ -8467,12 +7784,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>33846</t>
+          <t>33234</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>57680</t>
+          <t>58979</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -8482,12 +7799,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>29,74%</t>
+          <t>30,41%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -8502,12 +7819,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>19599</t>
+          <t>19373</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>41059</t>
+          <t>40343</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -8517,12 +7834,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -8537,12 +7854,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>58705</t>
+          <t>59301</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>91257</t>
+          <t>91019</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -8552,12 +7869,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>23,24%</t>
         </is>
       </c>
     </row>
@@ -8580,12 +7897,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>20456</t>
+          <t>20057</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>40004</t>
+          <t>39595</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -8595,12 +7912,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -8615,12 +7932,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>28814</t>
+          <t>29482</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>51961</t>
+          <t>52087</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -8630,12 +7947,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>26,36%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -8650,12 +7967,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>54059</t>
+          <t>54439</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>84642</t>
+          <t>85635</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8665,12 +7982,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>21,87%</t>
         </is>
       </c>
     </row>
@@ -8693,12 +8010,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>37630</t>
+          <t>37141</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>62508</t>
+          <t>61507</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8708,12 +8025,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>31,71%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8728,12 +8045,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>36974</t>
+          <t>38457</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>61662</t>
+          <t>62611</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8743,12 +8060,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>31,68%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8763,12 +8080,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>79875</t>
+          <t>82103</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>114869</t>
+          <t>117957</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8778,12 +8095,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>29,33%</t>
+          <t>30,12%</t>
         </is>
       </c>
     </row>
@@ -8806,12 +8123,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>16623</t>
+          <t>16332</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>36265</t>
+          <t>36065</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8821,12 +8138,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>18,59%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8841,12 +8158,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>30157</t>
+          <t>28797</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>55461</t>
+          <t>52697</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8856,12 +8173,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>28,06%</t>
+          <t>26,67%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8876,12 +8193,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>52926</t>
+          <t>51215</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>82517</t>
+          <t>81073</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8891,12 +8208,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>20,7%</t>
         </is>
       </c>
     </row>
@@ -8919,12 +8236,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>34228</t>
+          <t>35554</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>58124</t>
+          <t>61578</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8934,12 +8251,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>29,97%</t>
+          <t>31,75%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8954,12 +8271,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>30275</t>
+          <t>30378</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>52795</t>
+          <t>51853</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8969,12 +8286,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>26,24%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8989,12 +8306,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>70718</t>
+          <t>71417</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>104399</t>
+          <t>104791</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -9004,12 +8321,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>26,76%</t>
         </is>
       </c>
     </row>
@@ -9129,7 +8446,7 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -9139,107 +8456,107 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>139</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>154140</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>130460</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>177202</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>107</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>109992</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>91768</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>130932</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>246</t>
         </is>
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>264132</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>231536</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>294430</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>11,98%</t>
         </is>
       </c>
     </row>
@@ -9252,107 +8569,107 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>176</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>187440</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>162868</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>216988</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>146</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>150403</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>129196</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>175383</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>322</t>
         </is>
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>337843</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>303940</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>372851</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>15,17%</t>
         </is>
       </c>
     </row>
@@ -9365,107 +8682,107 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>349</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>376194</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>342700</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>411205</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>26,45%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>24,09%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>28,91%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>266</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>264690</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>237371</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>293641</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>25,54%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>22,91%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>28,34%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>615</t>
         </is>
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>640885</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>592789</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>683883</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>26,07%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>24,11%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>27,82%</t>
         </is>
       </c>
     </row>
@@ -9478,107 +8795,107 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>305</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>321151</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>290987</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>353453</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>22,58%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>24,85%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>232</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>236082</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>207916</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>264458</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>22,78%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>25,52%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>537</t>
         </is>
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>557233</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>517737</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>602716</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>24,52%</t>
         </is>
       </c>
     </row>
@@ -9591,107 +8908,107 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>354</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>383397</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>348712</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>421042</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>26,96%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>24,52%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>29,6%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>261</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>275051</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>241962</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>304950</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>26,54%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>23,35%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>29,43%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>615</t>
         </is>
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>658448</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>610085</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>704636</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>26,78%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>24,81%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>28,66%</t>
         </is>
       </c>
     </row>
@@ -9704,804 +9021,121 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1323</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1422322</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1422322</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1422322</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1012</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1036219</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1036219</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1036219</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2335</t>
         </is>
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2458541</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2458541</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2458541</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B40" s="3" t="inlineStr">
-        <is>
-          <t>Nunca</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>154140</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>130281</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>181842</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>10,84%</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>9,16%</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>12,78%</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t>109992</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="inlineStr">
-        <is>
-          <t>91499</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr">
-        <is>
-          <t>131048</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="inlineStr">
-        <is>
-          <t>10,61%</t>
-        </is>
-      </c>
-      <c r="O40" s="2" t="inlineStr">
-        <is>
-          <t>8,83%</t>
-        </is>
-      </c>
-      <c r="P40" s="2" t="inlineStr">
-        <is>
-          <t>12,65%</t>
-        </is>
-      </c>
-      <c r="Q40" s="2" t="inlineStr">
-        <is>
-          <t>246</t>
-        </is>
-      </c>
-      <c r="R40" s="2" t="inlineStr">
-        <is>
-          <t>264132</t>
-        </is>
-      </c>
-      <c r="S40" s="2" t="inlineStr">
-        <is>
-          <t>234501</t>
-        </is>
-      </c>
-      <c r="T40" s="2" t="inlineStr">
-        <is>
-          <t>296264</t>
-        </is>
-      </c>
-      <c r="U40" s="2" t="inlineStr">
-        <is>
-          <t>10,74%</t>
-        </is>
-      </c>
-      <c r="V40" s="2" t="inlineStr">
-        <is>
-          <t>9,54%</t>
-        </is>
-      </c>
-      <c r="W40" s="2" t="inlineStr">
-        <is>
-          <t>12,05%</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="1" t="n"/>
-      <c r="B41" s="3" t="inlineStr">
-        <is>
-          <t>Solo alguna vez</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>187440</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>162647</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>214470</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>13,18%</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>11,44%</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>15,08%</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>146</t>
-        </is>
-      </c>
-      <c r="K41" s="2" t="inlineStr">
-        <is>
-          <t>150403</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="inlineStr">
-        <is>
-          <t>127738</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr">
-        <is>
-          <t>173183</t>
-        </is>
-      </c>
-      <c r="N41" s="2" t="inlineStr">
-        <is>
-          <t>14,51%</t>
-        </is>
-      </c>
-      <c r="O41" s="2" t="inlineStr">
-        <is>
-          <t>12,33%</t>
-        </is>
-      </c>
-      <c r="P41" s="2" t="inlineStr">
-        <is>
-          <t>16,71%</t>
-        </is>
-      </c>
-      <c r="Q41" s="2" t="inlineStr">
-        <is>
-          <t>322</t>
-        </is>
-      </c>
-      <c r="R41" s="2" t="inlineStr">
-        <is>
-          <t>337843</t>
-        </is>
-      </c>
-      <c r="S41" s="2" t="inlineStr">
-        <is>
-          <t>301550</t>
-        </is>
-      </c>
-      <c r="T41" s="2" t="inlineStr">
-        <is>
-          <t>372254</t>
-        </is>
-      </c>
-      <c r="U41" s="2" t="inlineStr">
-        <is>
-          <t>13,74%</t>
-        </is>
-      </c>
-      <c r="V41" s="2" t="inlineStr">
-        <is>
-          <t>12,27%</t>
-        </is>
-      </c>
-      <c r="W41" s="2" t="inlineStr">
-        <is>
-          <t>15,14%</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="1" t="n"/>
-      <c r="B42" s="3" t="inlineStr">
-        <is>
-          <t>Algunas veces</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>349</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>376194</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>343032</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>412705</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>26,45%</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>24,12%</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>29,02%</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>266</t>
-        </is>
-      </c>
-      <c r="K42" s="2" t="inlineStr">
-        <is>
-          <t>264690</t>
-        </is>
-      </c>
-      <c r="L42" s="2" t="inlineStr">
-        <is>
-          <t>237856</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr">
-        <is>
-          <t>291458</t>
-        </is>
-      </c>
-      <c r="N42" s="2" t="inlineStr">
-        <is>
-          <t>25,54%</t>
-        </is>
-      </c>
-      <c r="O42" s="2" t="inlineStr">
-        <is>
-          <t>22,95%</t>
-        </is>
-      </c>
-      <c r="P42" s="2" t="inlineStr">
-        <is>
-          <t>28,13%</t>
-        </is>
-      </c>
-      <c r="Q42" s="2" t="inlineStr">
-        <is>
-          <t>615</t>
-        </is>
-      </c>
-      <c r="R42" s="2" t="inlineStr">
-        <is>
-          <t>640885</t>
-        </is>
-      </c>
-      <c r="S42" s="2" t="inlineStr">
-        <is>
-          <t>599321</t>
-        </is>
-      </c>
-      <c r="T42" s="2" t="inlineStr">
-        <is>
-          <t>690610</t>
-        </is>
-      </c>
-      <c r="U42" s="2" t="inlineStr">
-        <is>
-          <t>26,07%</t>
-        </is>
-      </c>
-      <c r="V42" s="2" t="inlineStr">
-        <is>
-          <t>24,38%</t>
-        </is>
-      </c>
-      <c r="W42" s="2" t="inlineStr">
-        <is>
-          <t>28,09%</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="1" t="n"/>
-      <c r="B43" s="3" t="inlineStr">
-        <is>
-          <t>Muchas veces</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>305</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>321151</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>285910</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>352403</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>22,58%</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>20,1%</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>24,78%</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>232</t>
-        </is>
-      </c>
-      <c r="K43" s="2" t="inlineStr">
-        <is>
-          <t>236082</t>
-        </is>
-      </c>
-      <c r="L43" s="2" t="inlineStr">
-        <is>
-          <t>209252</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr">
-        <is>
-          <t>262593</t>
-        </is>
-      </c>
-      <c r="N43" s="2" t="inlineStr">
-        <is>
-          <t>22,78%</t>
-        </is>
-      </c>
-      <c r="O43" s="2" t="inlineStr">
-        <is>
-          <t>20,19%</t>
-        </is>
-      </c>
-      <c r="P43" s="2" t="inlineStr">
-        <is>
-          <t>25,34%</t>
-        </is>
-      </c>
-      <c r="Q43" s="2" t="inlineStr">
-        <is>
-          <t>537</t>
-        </is>
-      </c>
-      <c r="R43" s="2" t="inlineStr">
-        <is>
-          <t>557233</t>
-        </is>
-      </c>
-      <c r="S43" s="2" t="inlineStr">
-        <is>
-          <t>516819</t>
-        </is>
-      </c>
-      <c r="T43" s="2" t="inlineStr">
-        <is>
-          <t>599337</t>
-        </is>
-      </c>
-      <c r="U43" s="2" t="inlineStr">
-        <is>
-          <t>22,67%</t>
-        </is>
-      </c>
-      <c r="V43" s="2" t="inlineStr">
-        <is>
-          <t>21,02%</t>
-        </is>
-      </c>
-      <c r="W43" s="2" t="inlineStr">
-        <is>
-          <t>24,38%</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="1" t="n"/>
-      <c r="B44" s="3" t="inlineStr">
-        <is>
-          <t>Siempre</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>354</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>383397</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>350384</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>419491</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>26,96%</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>24,63%</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>29,49%</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>261</t>
-        </is>
-      </c>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t>275051</t>
-        </is>
-      </c>
-      <c r="L44" s="2" t="inlineStr">
-        <is>
-          <t>248085</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr">
-        <is>
-          <t>307942</t>
-        </is>
-      </c>
-      <c r="N44" s="2" t="inlineStr">
-        <is>
-          <t>26,54%</t>
-        </is>
-      </c>
-      <c r="O44" s="2" t="inlineStr">
-        <is>
-          <t>23,94%</t>
-        </is>
-      </c>
-      <c r="P44" s="2" t="inlineStr">
-        <is>
-          <t>29,72%</t>
-        </is>
-      </c>
-      <c r="Q44" s="2" t="inlineStr">
-        <is>
-          <t>615</t>
-        </is>
-      </c>
-      <c r="R44" s="2" t="inlineStr">
-        <is>
-          <t>658448</t>
-        </is>
-      </c>
-      <c r="S44" s="2" t="inlineStr">
-        <is>
-          <t>616842</t>
-        </is>
-      </c>
-      <c r="T44" s="2" t="inlineStr">
-        <is>
-          <t>708408</t>
-        </is>
-      </c>
-      <c r="U44" s="2" t="inlineStr">
-        <is>
-          <t>26,78%</t>
-        </is>
-      </c>
-      <c r="V44" s="2" t="inlineStr">
-        <is>
-          <t>25,09%</t>
-        </is>
-      </c>
-      <c r="W44" s="2" t="inlineStr">
-        <is>
-          <t>28,81%</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="1" t="n"/>
-      <c r="B45" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>1323</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>1422322</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>1422322</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>1422322</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>1012</t>
-        </is>
-      </c>
-      <c r="K45" s="2" t="inlineStr">
-        <is>
-          <t>1036219</t>
-        </is>
-      </c>
-      <c r="L45" s="2" t="inlineStr">
-        <is>
-          <t>1036219</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr">
-        <is>
-          <t>1036219</t>
-        </is>
-      </c>
-      <c r="N45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q45" s="2" t="inlineStr">
-        <is>
-          <t>2335</t>
-        </is>
-      </c>
-      <c r="R45" s="2" t="inlineStr">
-        <is>
-          <t>2458541</t>
-        </is>
-      </c>
-      <c r="S45" s="2" t="inlineStr">
-        <is>
-          <t>2458541</t>
-        </is>
-      </c>
-      <c r="T45" s="2" t="inlineStr">
-        <is>
-          <t>2458541</t>
-        </is>
-      </c>
-      <c r="U45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
+      <c r="A40" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A22:A27"/>
-    <mergeCell ref="A40:A45"/>
     <mergeCell ref="A4:A9"/>
     <mergeCell ref="A16:A21"/>
     <mergeCell ref="A34:A39"/>

--- a/data/trans_orig/P6709-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P6709-Clase-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1772</t>
+          <t>1778</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11107</t>
+          <t>9781</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -751,7 +751,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2842</t>
+          <t>2950</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12832</t>
+          <t>12905</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6608</t>
+          <t>5851</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>20133</t>
+          <t>19501</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>3,92%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3678</t>
+          <t>3617</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16799</t>
+          <t>17867</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5971</t>
+          <t>5237</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>21074</t>
+          <t>20568</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>11785</t>
+          <t>11862</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>31174</t>
+          <t>32543</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,54%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>40130</t>
+          <t>40887</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>68538</t>
+          <t>67237</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>24092</t>
+          <t>24637</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>47523</t>
+          <t>47850</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>24,61%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>72981</t>
+          <t>73334</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>108920</t>
+          <t>109423</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>22,01%</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>60247</t>
+          <t>61583</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>92617</t>
+          <t>92155</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,59%</t>
+          <t>30,43%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1105,12 +1105,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>37725</t>
+          <t>37889</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>63472</t>
+          <t>63855</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1120,12 +1120,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>19,49%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>32,65%</t>
+          <t>32,84%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>106074</t>
+          <t>107101</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>146155</t>
+          <t>147077</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>21,54%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>29,39%</t>
+          <t>29,58%</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>145402</t>
+          <t>142714</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>180962</t>
+          <t>179542</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>48,02%</t>
+          <t>47,13%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>59,76%</t>
+          <t>59,29%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1218,12 +1218,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>75909</t>
+          <t>76560</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>104302</t>
+          <t>105012</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>39,05%</t>
+          <t>39,38%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>53,65%</t>
+          <t>54,01%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1253,12 +1253,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>228699</t>
+          <t>228680</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>274412</t>
+          <t>277037</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1268,12 +1268,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>46,0%</t>
+          <t>45,99%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>55,19%</t>
+          <t>55,72%</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9675</t>
+          <t>8876</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>29840</t>
+          <t>29545</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14918</t>
+          <t>14298</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>33606</t>
+          <t>32476</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>27616</t>
+          <t>27268</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>56018</t>
+          <t>54786</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,03%</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8847</t>
+          <t>7940</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>25406</t>
+          <t>25427</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1541,12 +1541,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7845</t>
+          <t>7908</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>25341</t>
+          <t>24064</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>19610</t>
+          <t>19836</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>43554</t>
+          <t>42758</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1611,12 +1611,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,17%</t>
         </is>
       </c>
     </row>
@@ -1639,12 +1639,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>44061</t>
+          <t>44871</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>72181</t>
+          <t>72636</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>28,14%</t>
+          <t>28,32%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>20334</t>
+          <t>20303</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>41375</t>
+          <t>42167</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>25,23%</t>
+          <t>25,71%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>69842</t>
+          <t>71723</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>106005</t>
+          <t>106702</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1724,12 +1724,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>25,37%</t>
         </is>
       </c>
     </row>
@@ -1752,12 +1752,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>63103</t>
+          <t>62952</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>95056</t>
+          <t>95464</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1767,12 +1767,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>24,54%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>37,06%</t>
+          <t>37,22%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1787,12 +1787,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>41609</t>
+          <t>40589</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>65913</t>
+          <t>65508</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1802,12 +1802,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>25,37%</t>
+          <t>24,75%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>40,19%</t>
+          <t>39,95%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1822,12 +1822,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>112887</t>
+          <t>112210</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>152420</t>
+          <t>152552</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>26,68%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>36,28%</t>
         </is>
       </c>
     </row>
@@ -1865,12 +1865,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>73083</t>
+          <t>73478</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>105059</t>
+          <t>104794</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1880,12 +1880,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>28,49%</t>
+          <t>28,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>40,96%</t>
+          <t>40,85%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>33515</t>
+          <t>33133</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>56049</t>
+          <t>56048</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1915,7 +1915,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1935,12 +1935,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>112628</t>
+          <t>111925</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>153638</t>
+          <t>154102</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1950,12 +1950,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>26,78%</t>
+          <t>26,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>36,54%</t>
+          <t>36,65%</t>
         </is>
       </c>
     </row>
@@ -2095,12 +2095,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4213</t>
+          <t>4339</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16014</t>
+          <t>15949</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1016</t>
+          <t>989</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10039</t>
+          <t>9968</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2145,12 +2145,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>7429</t>
+          <t>7183</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>22602</t>
+          <t>21717</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,57%</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12518</t>
+          <t>12273</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>28336</t>
+          <t>28852</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2223,12 +2223,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2248,7 +2248,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7109</t>
+          <t>6137</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>14661</t>
+          <t>14059</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>32334</t>
+          <t>32361</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,3%</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>37327</t>
+          <t>37281</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>64372</t>
+          <t>64013</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2336,12 +2336,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>22,9%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2356,12 +2356,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>7664</t>
+          <t>7698</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>22334</t>
+          <t>21948</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2391,12 +2391,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>47786</t>
+          <t>49231</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>78874</t>
+          <t>78515</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>20,13%</t>
         </is>
       </c>
     </row>
@@ -2434,12 +2434,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>51584</t>
+          <t>53590</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>79483</t>
+          <t>81434</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>28,43%</t>
+          <t>29,13%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7097</t>
+          <t>7132</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>21058</t>
+          <t>19185</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>63117</t>
+          <t>64625</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>94765</t>
+          <t>94975</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>24,35%</t>
         </is>
       </c>
     </row>
@@ -2547,12 +2547,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>118192</t>
+          <t>119423</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>152594</t>
+          <t>151287</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2562,12 +2562,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>42,28%</t>
+          <t>42,72%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>54,58%</t>
+          <t>54,11%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2582,12 +2582,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>69981</t>
+          <t>68515</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>87934</t>
+          <t>86979</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2597,12 +2597,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>63,32%</t>
+          <t>61,99%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>79,56%</t>
+          <t>78,7%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>193828</t>
+          <t>193097</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>233970</t>
+          <t>232067</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2632,12 +2632,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>49,69%</t>
+          <t>49,5%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>59,98%</t>
+          <t>59,49%</t>
         </is>
       </c>
     </row>
@@ -2777,12 +2777,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>29551</t>
+          <t>29147</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>55001</t>
+          <t>55979</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2812,12 +2812,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>24667</t>
+          <t>23693</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>47479</t>
+          <t>45818</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2847,12 +2847,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>58869</t>
+          <t>57381</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>92513</t>
+          <t>91850</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>12,74%</t>
         </is>
       </c>
     </row>
@@ -2890,12 +2890,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>25527</t>
+          <t>27061</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>51879</t>
+          <t>51079</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2905,12 +2905,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2925,12 +2925,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>13866</t>
+          <t>13612</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>34188</t>
+          <t>33678</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2940,12 +2940,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2960,12 +2960,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>45804</t>
+          <t>45905</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>78334</t>
+          <t>78963</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2975,12 +2975,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,95%</t>
         </is>
       </c>
     </row>
@@ -3003,12 +3003,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>82385</t>
+          <t>81747</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>118767</t>
+          <t>116925</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3018,12 +3018,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>19,28%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>28,01%</t>
+          <t>27,57%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>63321</t>
+          <t>61468</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>92319</t>
+          <t>93372</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3053,12 +3053,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>20,71%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>31,1%</t>
+          <t>31,46%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>153027</t>
+          <t>152448</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>202733</t>
+          <t>200604</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3088,12 +3088,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>28,12%</t>
+          <t>27,83%</t>
         </is>
       </c>
     </row>
@@ -3116,12 +3116,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>85940</t>
+          <t>84493</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>119633</t>
+          <t>122036</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3131,12 +3131,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>19,92%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>28,78%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>49495</t>
+          <t>49378</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>77711</t>
+          <t>76841</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>25,89%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>141456</t>
+          <t>142009</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>186670</t>
+          <t>188330</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>26,12%</t>
         </is>
       </c>
     </row>
@@ -3229,12 +3229,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>124294</t>
+          <t>123205</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>163631</t>
+          <t>165808</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3244,12 +3244,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>29,05%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>38,59%</t>
+          <t>39,1%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3264,12 +3264,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>85897</t>
+          <t>86305</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>119361</t>
+          <t>118813</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>28,94%</t>
+          <t>29,08%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>40,21%</t>
+          <t>40,03%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>220908</t>
+          <t>219642</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>274723</t>
+          <t>272555</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>30,64%</t>
+          <t>30,47%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>38,11%</t>
+          <t>37,81%</t>
         </is>
       </c>
     </row>
@@ -3459,12 +3459,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>17146</t>
+          <t>17605</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>35767</t>
+          <t>35907</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3474,12 +3474,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>23,78%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>15860</t>
+          <t>16003</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>33914</t>
+          <t>36420</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3509,12 +3509,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>20,86%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>38111</t>
+          <t>37323</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>64487</t>
+          <t>64723</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>19,88%</t>
         </is>
       </c>
     </row>
@@ -3572,12 +3572,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>11795</t>
+          <t>11439</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>27647</t>
+          <t>28433</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3587,12 +3587,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>18,83%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3607,12 +3607,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>10923</t>
+          <t>9700</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>28330</t>
+          <t>27550</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3642,12 +3642,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>26310</t>
+          <t>25956</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>49195</t>
+          <t>49168</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>15,1%</t>
         </is>
       </c>
     </row>
@@ -3685,12 +3685,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>26073</t>
+          <t>25654</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>47240</t>
+          <t>48400</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>31,29%</t>
+          <t>32,06%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3720,12 +3720,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>29078</t>
+          <t>28611</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>52524</t>
+          <t>52608</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>30,13%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3755,12 +3755,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>61694</t>
+          <t>61316</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>92323</t>
+          <t>94528</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>18,83%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>28,36%</t>
+          <t>29,03%</t>
         </is>
       </c>
     </row>
@@ -3798,12 +3798,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>24183</t>
+          <t>25043</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>45282</t>
+          <t>45873</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3813,12 +3813,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>29,99%</t>
+          <t>30,38%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>24140</t>
+          <t>23727</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>45562</t>
+          <t>44236</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>25,34%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>54952</t>
+          <t>54305</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>85716</t>
+          <t>84396</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>26,33%</t>
+          <t>25,92%</t>
         </is>
       </c>
     </row>
@@ -3911,12 +3911,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>26090</t>
+          <t>25588</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>47398</t>
+          <t>47258</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3926,12 +3926,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>31,39%</t>
+          <t>31,3%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3946,12 +3946,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>45775</t>
+          <t>46198</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>72436</t>
+          <t>71765</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>26,46%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>41,49%</t>
+          <t>41,1%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3981,12 +3981,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>78154</t>
+          <t>77965</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>112245</t>
+          <t>111326</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>23,95%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>34,48%</t>
+          <t>34,19%</t>
         </is>
       </c>
     </row>
@@ -4141,12 +4141,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>78148</t>
+          <t>78124</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>118399</t>
+          <t>120454</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4176,12 +4176,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>71686</t>
+          <t>72877</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>110813</t>
+          <t>110186</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4211,12 +4211,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>163329</t>
+          <t>160822</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>219252</t>
+          <t>217210</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,23%</t>
         </is>
       </c>
     </row>
@@ -4254,12 +4254,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>81554</t>
+          <t>79240</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>119531</t>
+          <t>120294</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4269,12 +4269,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4289,12 +4289,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>51743</t>
+          <t>53263</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>88337</t>
+          <t>86770</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4304,12 +4304,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4324,12 +4324,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>141974</t>
+          <t>146056</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>195651</t>
+          <t>197377</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,38%</t>
         </is>
       </c>
     </row>
@@ -4367,12 +4367,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>264048</t>
+          <t>266200</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>329847</t>
+          <t>329156</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4382,12 +4382,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>18,83%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>23,28%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4402,12 +4402,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>169162</t>
+          <t>170709</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>223138</t>
+          <t>224412</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>23,86%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4437,12 +4437,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>449692</t>
+          <t>450901</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>533137</t>
+          <t>535863</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>22,76%</t>
         </is>
       </c>
     </row>
@@ -4480,12 +4480,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>323291</t>
+          <t>323562</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>393347</t>
+          <t>389976</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4495,12 +4495,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>22,88%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>27,82%</t>
+          <t>27,58%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>186191</t>
+          <t>186581</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>237077</t>
+          <t>236972</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4530,12 +4530,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>25,2%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4550,12 +4550,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>525727</t>
+          <t>524110</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>606867</t>
+          <t>609941</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4565,12 +4565,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>22,26%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>25,78%</t>
+          <t>25,91%</t>
         </is>
       </c>
     </row>
@@ -4593,12 +4593,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>526995</t>
+          <t>527795</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>603724</t>
+          <t>605674</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>37,27%</t>
+          <t>37,33%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>42,7%</t>
+          <t>42,84%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4628,12 +4628,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>343983</t>
+          <t>340818</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>405738</t>
+          <t>404481</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4643,12 +4643,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>36,58%</t>
+          <t>36,24%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>43,15%</t>
+          <t>43,01%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4663,12 +4663,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>893456</t>
+          <t>889055</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>989120</t>
+          <t>987087</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>37,95%</t>
+          <t>37,76%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>42,01%</t>
+          <t>41,93%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4928</t>
+          <t>4252</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17895</t>
+          <t>18832</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5122</t>
+          <t>5593</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18863</t>
+          <t>19617</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12337</t>
+          <t>11953</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>30865</t>
+          <t>30171</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,13%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11394</t>
+          <t>10877</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>29681</t>
+          <t>28981</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13089</t>
+          <t>12577</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>31520</t>
+          <t>29196</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>27664</t>
+          <t>28221</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>52651</t>
+          <t>53386</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,84%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>61448</t>
+          <t>62497</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>92584</t>
+          <t>93503</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>22,45%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>33,26%</t>
+          <t>33,59%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>35923</t>
+          <t>34380</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>60588</t>
+          <t>58218</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>27,18%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>105726</t>
+          <t>103546</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>144290</t>
+          <t>144130</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>29,3%</t>
+          <t>29,26%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>50602</t>
+          <t>50216</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>79497</t>
+          <t>79347</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,56%</t>
+          <t>28,51%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>52253</t>
+          <t>52135</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>78548</t>
+          <t>78757</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>24,34%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>36,67%</t>
+          <t>36,77%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>109512</t>
+          <t>107926</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>148283</t>
+          <t>147454</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>21,91%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>30,11%</t>
+          <t>29,94%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>91827</t>
+          <t>91469</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>125913</t>
+          <t>125486</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>32,99%</t>
+          <t>32,86%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>45,24%</t>
+          <t>45,08%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>58570</t>
+          <t>57557</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>86416</t>
+          <t>86962</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>26,87%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>40,35%</t>
+          <t>40,6%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>159579</t>
+          <t>160274</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>204549</t>
+          <t>203684</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>32,4%</t>
+          <t>32,54%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>41,53%</t>
+          <t>41,36%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9584</t>
+          <t>10814</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>28012</t>
+          <t>28272</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>13594</t>
+          <t>13199</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>30817</t>
+          <t>30119</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>27061</t>
+          <t>27905</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>51853</t>
+          <t>54740</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>12,64%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>33014</t>
+          <t>32894</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>57320</t>
+          <t>57653</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>23,63%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>27953</t>
+          <t>28399</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>50739</t>
+          <t>51405</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>26,82%</t>
+          <t>27,17%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>66106</t>
+          <t>67390</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>100617</t>
+          <t>100199</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>23,13%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>45745</t>
+          <t>46226</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>73077</t>
+          <t>72410</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>29,95%</t>
+          <t>29,67%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>32796</t>
+          <t>33821</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>56549</t>
+          <t>56914</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>29,89%</t>
+          <t>30,09%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>86077</t>
+          <t>86134</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>122179</t>
+          <t>124001</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>19,88%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>28,62%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>51756</t>
+          <t>51387</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>82156</t>
+          <t>80661</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>33,67%</t>
+          <t>33,05%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>36955</t>
+          <t>36762</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>60809</t>
+          <t>61828</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,14%</t>
+          <t>32,68%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>95160</t>
+          <t>96458</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>135134</t>
+          <t>134103</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,19%</t>
+          <t>30,96%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>44009</t>
+          <t>44251</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>69804</t>
+          <t>72950</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6205,12 +6205,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>29,89%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>27130</t>
+          <t>27262</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>49750</t>
+          <t>49880</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>26,3%</t>
+          <t>26,37%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>77651</t>
+          <t>78234</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>113591</t>
+          <t>111908</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>25,83%</t>
         </is>
       </c>
     </row>
@@ -6420,12 +6420,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6235</t>
+          <t>6123</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>19697</t>
+          <t>19988</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6435,12 +6435,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6460,7 +6460,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4830</t>
+          <t>4970</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6475,7 +6475,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>7425</t>
+          <t>6467</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>22840</t>
+          <t>20826</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6505,12 +6505,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>7,32%</t>
         </is>
       </c>
     </row>
@@ -6533,12 +6533,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13360</t>
+          <t>13400</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>31223</t>
+          <t>32112</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6548,12 +6548,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>850</t>
+          <t>840</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7854</t>
+          <t>8660</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>16149</t>
+          <t>16824</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>35851</t>
+          <t>35833</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6618,7 +6618,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -6646,12 +6646,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>39741</t>
+          <t>39181</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>65532</t>
+          <t>65071</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6661,12 +6661,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>30,16%</t>
+          <t>29,95%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>5107</t>
+          <t>5325</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>17112</t>
+          <t>17242</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6696,12 +6696,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>25,66%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>48754</t>
+          <t>49286</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>76036</t>
+          <t>78005</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6731,12 +6731,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>27,42%</t>
         </is>
       </c>
     </row>
@@ -6759,12 +6759,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>46873</t>
+          <t>47372</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>72977</t>
+          <t>74196</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>21,8%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>33,59%</t>
+          <t>34,15%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6794,12 +6794,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8468</t>
+          <t>8101</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>22012</t>
+          <t>22074</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6809,12 +6809,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>32,76%</t>
+          <t>32,85%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6829,12 +6829,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>59896</t>
+          <t>59877</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>91177</t>
+          <t>89100</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6844,12 +6844,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>32,05%</t>
+          <t>31,32%</t>
         </is>
       </c>
     </row>
@@ -6872,12 +6872,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>59366</t>
+          <t>58487</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>87782</t>
+          <t>88352</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>27,32%</t>
+          <t>26,92%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>40,4%</t>
+          <t>40,67%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6907,12 +6907,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>30348</t>
+          <t>30290</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>46487</t>
+          <t>46680</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6922,12 +6922,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>45,16%</t>
+          <t>45,07%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>69,18%</t>
+          <t>69,46%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6942,12 +6942,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>94647</t>
+          <t>95112</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>128725</t>
+          <t>127380</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6957,12 +6957,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>33,27%</t>
+          <t>33,44%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>45,25%</t>
+          <t>44,78%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>56280</t>
+          <t>53738</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>86579</t>
+          <t>86408</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>37786</t>
+          <t>38031</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>64418</t>
+          <t>63342</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7152,12 +7152,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>98005</t>
+          <t>101776</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>138836</t>
+          <t>141647</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>16,53%</t>
         </is>
       </c>
     </row>
@@ -7215,12 +7215,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>58616</t>
+          <t>59598</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>91200</t>
+          <t>91976</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7250,12 +7250,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>39024</t>
+          <t>37630</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>65557</t>
+          <t>65001</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7265,12 +7265,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -7285,12 +7285,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>104230</t>
+          <t>104726</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>144389</t>
+          <t>149322</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -7300,12 +7300,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>17,43%</t>
         </is>
       </c>
     </row>
@@ -7328,12 +7328,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>122116</t>
+          <t>119665</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>163031</t>
+          <t>160907</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>24,49%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>33,36%</t>
+          <t>32,92%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -7363,12 +7363,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>99236</t>
+          <t>97995</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>132212</t>
+          <t>132601</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -7378,12 +7378,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>26,96%</t>
+          <t>26,63%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>35,92%</t>
+          <t>36,03%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -7398,12 +7398,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>230113</t>
+          <t>231194</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>283371</t>
+          <t>284120</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -7413,12 +7413,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>26,86%</t>
+          <t>26,98%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>33,07%</t>
+          <t>33,16%</t>
         </is>
       </c>
     </row>
@@ -7441,12 +7441,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>88931</t>
+          <t>89122</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>125391</t>
+          <t>125585</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7456,12 +7456,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>25,7%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7476,12 +7476,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>54213</t>
+          <t>53904</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>82991</t>
+          <t>82384</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7511,12 +7511,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>151446</t>
+          <t>149796</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>196951</t>
+          <t>198009</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>23,11%</t>
         </is>
       </c>
     </row>
@@ -7554,12 +7554,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>82182</t>
+          <t>81400</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>118067</t>
+          <t>117275</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7569,12 +7569,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7589,12 +7589,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>71454</t>
+          <t>71166</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>103664</t>
+          <t>103435</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>28,1%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7624,12 +7624,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>161393</t>
+          <t>159209</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>212060</t>
+          <t>209705</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>24,48%</t>
         </is>
       </c>
     </row>
@@ -7784,12 +7784,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>33234</t>
+          <t>33327</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>58979</t>
+          <t>57839</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7799,12 +7799,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>30,41%</t>
+          <t>29,82%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7819,12 +7819,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>19373</t>
+          <t>20038</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>40343</t>
+          <t>40292</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7834,12 +7834,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>20,39%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7854,12 +7854,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>59301</t>
+          <t>59498</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>91019</t>
+          <t>90514</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7869,12 +7869,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>23,11%</t>
         </is>
       </c>
     </row>
@@ -7897,12 +7897,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>20057</t>
+          <t>19659</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>39595</t>
+          <t>39468</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7912,12 +7912,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7932,12 +7932,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>29482</t>
+          <t>28908</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>52087</t>
+          <t>50958</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7947,12 +7947,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>25,79%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7967,12 +7967,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>54439</t>
+          <t>52483</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>85635</t>
+          <t>84218</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7982,12 +7982,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>21,51%</t>
         </is>
       </c>
     </row>
@@ -8010,12 +8010,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>37141</t>
+          <t>36998</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>61507</t>
+          <t>61670</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8025,12 +8025,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>31,71%</t>
+          <t>31,79%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8045,12 +8045,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>38457</t>
+          <t>38037</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>62611</t>
+          <t>61797</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8060,12 +8060,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>31,68%</t>
+          <t>31,27%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>82103</t>
+          <t>81470</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>117957</t>
+          <t>116014</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8095,12 +8095,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>30,12%</t>
+          <t>29,63%</t>
         </is>
       </c>
     </row>
@@ -8123,12 +8123,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>16332</t>
+          <t>16436</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>36065</t>
+          <t>35606</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8138,12 +8138,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8158,12 +8158,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>28797</t>
+          <t>29817</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>52697</t>
+          <t>53029</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8173,12 +8173,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>26,67%</t>
+          <t>26,83%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>51215</t>
+          <t>52674</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>81073</t>
+          <t>82132</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8208,12 +8208,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>20,97%</t>
         </is>
       </c>
     </row>
@@ -8236,12 +8236,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>35554</t>
+          <t>35138</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>61578</t>
+          <t>59332</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8251,12 +8251,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>31,75%</t>
+          <t>30,59%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8271,12 +8271,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>30378</t>
+          <t>29759</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>51853</t>
+          <t>52100</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8286,12 +8286,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>26,36%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8306,12 +8306,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>71417</t>
+          <t>71428</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>104791</t>
+          <t>105032</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8326,7 +8326,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>26,82%</t>
         </is>
       </c>
     </row>
@@ -8466,12 +8466,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>130460</t>
+          <t>130973</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>177202</t>
+          <t>180669</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8481,12 +8481,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8501,12 +8501,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>91768</t>
+          <t>92085</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>130932</t>
+          <t>131790</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8516,12 +8516,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>231536</t>
+          <t>234039</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>294430</t>
+          <t>297474</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>12,1%</t>
         </is>
       </c>
     </row>
@@ -8579,12 +8579,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>162868</t>
+          <t>164250</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>216988</t>
+          <t>215049</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -8594,12 +8594,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -8614,12 +8614,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>129196</t>
+          <t>128598</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>175383</t>
+          <t>176354</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -8629,12 +8629,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -8649,12 +8649,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>303940</t>
+          <t>304140</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>372851</t>
+          <t>373008</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -8664,7 +8664,7 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
@@ -8692,12 +8692,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>342700</t>
+          <t>341734</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>411205</t>
+          <t>409792</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -8707,12 +8707,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>28,81%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -8727,12 +8727,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>237371</t>
+          <t>239876</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>293641</t>
+          <t>292471</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -8742,12 +8742,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>23,15%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>28,22%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -8762,12 +8762,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>592789</t>
+          <t>597912</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>683883</t>
+          <t>685738</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -8777,12 +8777,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>27,82%</t>
+          <t>27,89%</t>
         </is>
       </c>
     </row>
@@ -8805,12 +8805,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>290987</t>
+          <t>289668</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>353453</t>
+          <t>351943</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -8820,12 +8820,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>20,37%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>24,74%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>207916</t>
+          <t>212355</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>264458</t>
+          <t>267163</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -8855,12 +8855,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>25,52%</t>
+          <t>25,78%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -8875,12 +8875,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>517737</t>
+          <t>517345</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>602716</t>
+          <t>600458</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -8890,12 +8890,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>24,42%</t>
         </is>
       </c>
     </row>
@@ -8918,12 +8918,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>348712</t>
+          <t>350620</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>421042</t>
+          <t>417421</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -8933,12 +8933,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>24,65%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>29,6%</t>
+          <t>29,35%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -8953,12 +8953,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>241962</t>
+          <t>246412</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>304950</t>
+          <t>305263</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -8968,12 +8968,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>23,78%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>29,46%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -8988,12 +8988,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>610085</t>
+          <t>614238</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>704636</t>
+          <t>704421</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>24,98%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>28,66%</t>
+          <t>28,65%</t>
         </is>
       </c>
     </row>
